--- a/extenbooks/ES1502.xlsx
+++ b/extenbooks/ES1502.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -989,7 +989,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1502 — Managerial Unproductive Labor (Mohun 2013) — PENDING</t>
+          <t># ES1502 — Managerial Unproductive Labor (Mohun 2013)</t>
         </is>
       </c>
     </row>
@@ -1001,87 +1001,31 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: book_period_validated. Source: same Mohun decomposition CSV, column `Lum_mohun`. 1948=7,669K; 1989=31,307K. Captures managerial/supervisory workers per Mohun's class decomposition.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Mohun decomposition</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Same source, managerial column</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1502.xlsx
+++ b/extenbooks/ES1502.xlsx
@@ -825,11 +825,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -876,7 +876,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 6</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–1989</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -978,52 +978,73 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1502-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mohun 2013 RRPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1502 — Managerial Unproductive Labor (Mohun 2013)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: book_period_validated. Source: same Mohun decomposition CSV, column `Lum_mohun`. 1948=7,669K; 1989=31,307K. Captures managerial/supervisory workers per Mohun's class decomposition.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1502 — Managerial Unproductive Labor (Mohun 2013)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1040,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1068,155 +1089,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Managerial unproductive labor = supervisory labor (managers-plus-capitalists), defined as workers whose function is the authoritarian control and supervision of the working class. Identification criterion: those whose work involves controlling the work of others. Operationally computed as NIPA total employment minus working class (CES production worker) employment, by sector. This subtraction allocates all wages missing from the CES survey — stock options, bonuses, retroactive pay, and other irregular compensation — to supervisory workers. The paper does NOT separately identify capitalists from managers; they are treated together as 'managers-plus-capitalists.'</t>
+          <t>Marxist approaches that focus on productive and unproductive labor have in fact been both misled and misleading because they have treated "wages" as the income of labor and "profits" as the income of capital in a historical era in which managers-plus-capitalists have taken more and more surplus-value as labor income rather than as profit, financed since 1979 by a large increase in the rate of surplus-value.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 2.1 and 4.2 and Appendix; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Supervisory employment share of total employment: 1964 = 16.8%; peak 1991 = 19.9%; 2010 = 17.9%. Not a great deal of variation — fluctuates within a 3 percentage point band (after 1973, within 2 points). Supervisory WAGE share of total wages: 1964 = ~32%; 1979 = 35.1%; 1979-1992 = extraordinary increase of ~11 percentage points; peak 2007 = 47.8%; 2010 = 46.6%. This dramatic decoupling of employment share (flat) from wage share (soaring) is the central empirical finding of Mohun (2013).</t>
+          <t>But from 1979 onwards this was not the case; the relatively large increase in value added absorbed by supervisory wages was financed by a large fall in the value of labor-power (large increase in the rate of surplus-value). This can only be considered a burden if it is thought that this rise in the rate of surplus-value "should" have found its way into an increased profit share.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 4.2, Fig 3; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>value_added_absorption</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Supervisory wages as share of money value added (Y): 1964 = 22.1%; 2000 = 35.5% (peak, +60% increase); 2010 = ~34%. Between 1978 and 1992 most of the increase occurred. By 2000, some 13.5 percentage points less of value added was available for working class wages and profits compared to 1964. The entire rise was financed by a fall in the value of labor-power (rise in the rate of surplus value) after 1979 — not at the expense of working class wages (which had a stable VA share), but at the expense of the profit share plus labor-power value.</t>
+          <t>Separating "pure" organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive, and the same practice is followed here.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 5, Fig 4; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>class_boundary_definition</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mohun states: 'In all processes involving capital and wage labor, capitalists hire managers to organize activities and to supervise in order that those activities are satisfactorily performed. These processes are typically hierarchical and authoritarian, with significant pay differentials that increase up the hierarchy. Separating pure organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive... It makes little conceptual sense to say that the policing of the capital relation in production and circulation processes by the agents of capital directly creates value.' Reference to Moseley (1991: 35-6).</t>
+          <t>Difference in trends between relative numbers and relative wages: Attributed to "the information technologies of the 1980s [which] slowed down the growth rate of unproductive employment but not its wage share" (Paitaridis and Tsoulfidis 2012: 218).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 2.1; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>st_boundary_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This is the key classification difference between ST and Mohun that drives the ES1404 ratio (ST/Mohun ≈ 1.61). In ST (1994), production workers in service-producing industries are 'nonsupervisory employees' — but in Mining, Manufacturing, and Construction the BLS production worker category additionally excludes finance, trade, personnel, professional, and clerical workers (not just supervisors). Mohun's 2013 framework systematically identifies all supervisory labor across all sectors by subtraction, producing a larger unproductive sector. The 18.7% average supervisory share is what Mohun labels as ST's 'supervision' category — workers absent from the BLS production worker count but not because of sector location, rather because of function.</t>
+          <t>Footnote 13 - Phase Changes: It is these comparative rates of growth that underlie the "phase-changes" explored by Paitaridis and Tsoulfidis (2012).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 3, Appendix; full_transcription.md; ST_1994 methodology</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>construction_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Series registry construction: step 1 op=derive, formula='Lu × 0.187', inputs=['Mohun Lu'], output='ES1502-COMBINED'. This reflects the stable 18.7% managerial/supervisory share of total unproductive employment. Units: thousands of full-time equivalent employees. Period 1964-2010.</t>
+          <t>91.5 percent of the "missing" wage and salary accruals are in just six sectors, accounting for 36.1% of total employment, and these sectors are all, in terms of average pay relative to average pay in the whole nonfarm private economy, "richer" sectors of the economy.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Series registry ES1502; Mohun_2013, Section 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Managerial unproductive labor = supervisory labor (managers-plus-capitalists), defined as workers whose function is the authoritarian control and supervision of the working class. Identification criterion: those whose work involves controlling the work of others. Operationally computed as NIPA total employment minus working class (CES production worker) employment, by sector. This subtraction allocates all wages missing from the CES survey — stock options, bonuses, retroactive pay, and other irregular compensation — to supervisory workers. The paper does NOT separately identify capitalists from managers; they are treated together as 'managers-plus-capitalists.'</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 2.1 and 4.2 and Appendix; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Managerial/supervisory unproductive employment (Lu_sup = managers-plus-capitalists), 1964-2010. Derived as Mohun total unproductive Lu × 0.187 (stable supervisory share). Employment share flat (~16.8-19.9%). Wage share explodes from 32% (1964) to 47.8% (2007). VA absorption: 22.1% (1964) to 35.5% (2000). This is the category absent from ST's framework but central to Mohun's class analysis and the driver of the ST/Mohun exploitation rate ratio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Supervisory employment share of total employment: 1964 = 16.8%; peak 1991 = 19.9%; 2010 = 17.9%. Not a great deal of variation — fluctuates within a 3 percentage point band (after 1973, within 2 points). Supervisory WAGE share of total wages: 1964 = ~32%; 1979 = 35.1%; 1979-1992 = extraordinary increase of ~11 percentage points; peak 2007 = 47.8%; 2010 = 46.6%. This dramatic decoupling of employment share (flat) from wage share (soaring) is the central empirical finding of Mohun (2013).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 4.2, Fig 3; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>value_added_absorption</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supervisory wages as share of money value added (Y): 1964 = 22.1%; 2000 = 35.5% (peak, +60% increase); 2010 = ~34%. Between 1978 and 1992 most of the increase occurred. By 2000, some 13.5 percentage points less of value added was available for working class wages and profits compared to 1964. The entire rise was financed by a fall in the value of labor-power (rise in the rate of surplus value) after 1979 — not at the expense of working class wages (which had a stable VA share), but at the expense of the profit share plus labor-power value.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 5, Fig 4; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>class_boundary_definition</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mohun states: 'In all processes involving capital and wage labor, capitalists hire managers to organize activities and to supervise in order that those activities are satisfactorily performed. These processes are typically hierarchical and authoritarian, with significant pay differentials that increase up the hierarchy. Separating pure organization from authoritarian hierarchy and supervision is both theoretically doubtful and empirically impossible. The labor involved in such activities is conventionally treated as unproductive... It makes little conceptual sense to say that the policing of the capital relation in production and circulation processes by the agents of capital directly creates value.' Reference to Moseley (1991: 35-6).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 2.1; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>st_boundary_comparison</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Supervisory employment computed by subtraction — all CES-missing wages assigned to supervisors, including tips and payments-in-kind that may accrue to working class</t>
+          <t>This is the key classification difference between ST and Mohun that drives the ES1404 ratio (ST/Mohun ≈ 1.61). In ST (1994), production workers in service-producing industries are 'nonsupervisory employees' — but in Mining, Manufacturing, and Construction the BLS production worker category additionally excludes finance, trade, personnel, professional, and clerical workers (not just supervisors). Mohun's 2013 framework systematically identifies all supervisory labor across all sectors by subtraction, producing a larger unproductive sector. The 18.7% average supervisory share is what Mohun labels as ST's 'supervision' category — workers absent from the BLS production worker count but not because of sector location, rather because of function.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mohun_2013, Section 3, Appendix; full_transcription.md; ST_1994 methodology</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>construction_note</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cannot distinguish capitalists from managers within this aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Mining, Manufacturing, Construction 'supervisory' category includes some non-supervisors (finance, clerical, professional workers excluded from BLS production worker definition) — supervisory totals overestimated by indeterminate amount, decreasing as these sectors shrink</t>
-        </is>
-      </c>
-    </row>
+          <t>Series registry construction: step 1 op=derive, formula='Lu × 0.187', inputs=['Mohun Lu'], output='ES1502-COMBINED'. This reflects the stable 18.7% managerial/supervisory share of total unproductive employment. Units: thousands of full-time equivalent employees. Period 1964-2010.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Series registry ES1502; Mohun_2013, Section 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SIC-to-NAICS transition 1998 requires separate classification tables</t>
+          <t>Managerial/supervisory unproductive employment (Lu_sup = managers-plus-capitalists), 1964-2010. Derived as Mohun total unproductive Lu × 0.187 (stable supervisory share). Employment share flat (~16.8-19.9%). Wage share explodes from 32% (1964) to 47.8% (2007). VA absorption: 22.1% (1964) to 35.5% (2000). This is the category absent from ST's framework but central to Mohun's class analysis and the driver of the ST/Mohun exploitation rate ratio.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1307,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cross_references:</t>
+          <t>known_issues:</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1315,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES1501</t>
+          <t>Supervisory employment computed by subtraction — all CES-missing wages assigned to supervisors, including tips and payments-in-kind that may accrue to working class</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1323,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ES1503</t>
+          <t>Cannot distinguish capitalists from managers within this aggregate</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1331,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ES1504</t>
+          <t>Mining, Manufacturing, Construction 'supervisory' category includes some non-supervisors (finance, clerical, professional workers excluded from BLS production worker definition) — supervisory totals overestimated by indeterminate amount, decreasing as these sectors shrink</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1339,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ES1404</t>
+          <t>SIC-to-NAICS transition 1998 requires separate classification tables</t>
         </is>
       </c>
     </row>
@@ -1264,41 +1347,81 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ES1501</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ES1503</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ES1504</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES1404</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Mohun_2005</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1315,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1373,7 +1496,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lu Ã— 0.187</t>
+          <t>Lu — 0.187</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1530,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 7669.3547}</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1554,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dollar_series</t>
+          <t>level_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>level_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
     </row>
